--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_DOLAR.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_DOLAR.xlsx
@@ -2064,11 +2064,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="23420609"/>
-        <c:axId val="66453563"/>
+        <c:axId val="85098845"/>
+        <c:axId val="81143675"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="23420609"/>
+        <c:axId val="85098845"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2100,7 +2100,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66453563"/>
+        <c:crossAx val="81143675"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -2111,7 +2111,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="66453563"/>
+        <c:axId val="81143675"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="90"/>
@@ -2185,7 +2185,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="23420609"/>
+        <c:crossAx val="85098845"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="AH22" s="16" t="n">
         <f aca="false">+S23</f>
-        <v>-3.05235428999877</v>
+        <v>-2.92407267431875</v>
       </c>
       <c r="AI22" s="16"/>
       <c r="AJ22" s="16"/>
@@ -6333,7 +6333,7 @@
       <c r="AP22" s="16"/>
       <c r="AQ22" s="17" t="n">
         <f aca="false">+(B249/B246-1)/COUNTA(AE22:AP22)*12</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
       <c r="AV22" s="7"/>
       <c r="AW22" s="7"/>
@@ -6367,7 +6367,7 @@
       </c>
       <c r="S23" s="21" t="n">
         <f aca="false">LOOKUP(DATE($O23,S$25,S$24),$A$2:$A$2943,$C$2:$C$2943)</f>
-        <v>-3.05235428999877</v>
+        <v>-2.92407267431875</v>
       </c>
       <c r="T23" s="21"/>
       <c r="U23" s="21"/>
@@ -17628,15 +17628,15 @@
         <v>46142</v>
       </c>
       <c r="B249" s="4" t="n">
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="C249" s="25" t="n">
         <f aca="false">(B249/B248-1)/(A249-A248)*360</f>
-        <v>-3.05235428999877</v>
+        <v>-2.92407267431875</v>
       </c>
       <c r="D249" s="4" t="n">
         <f aca="false">B249/$B$3*100</f>
-        <v>179.266768079531</v>
+        <v>181.836900088812</v>
       </c>
       <c r="F249" s="18" t="n">
         <v>46142</v>

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_DOLAR.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_DOLAR.xlsx
@@ -2064,11 +2064,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="85098845"/>
-        <c:axId val="81143675"/>
+        <c:axId val="95583631"/>
+        <c:axId val="37101353"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="85098845"/>
+        <c:axId val="95583631"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2100,7 +2100,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81143675"/>
+        <c:crossAx val="37101353"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -2111,7 +2111,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="81143675"/>
+        <c:axId val="37101353"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="90"/>
@@ -2185,7 +2185,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85098845"/>
+        <c:crossAx val="95583631"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_DOLAR.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_DOLAR.xlsx
@@ -2064,11 +2064,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="95583631"/>
-        <c:axId val="37101353"/>
+        <c:axId val="48074097"/>
+        <c:axId val="85844360"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="95583631"/>
+        <c:axId val="48074097"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2100,7 +2100,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37101353"/>
+        <c:crossAx val="85844360"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -2111,7 +2111,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="37101353"/>
+        <c:axId val="85844360"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="90"/>
@@ -2185,7 +2185,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="95583631"/>
+        <c:crossAx val="48074097"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_DOLAR.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_DOLAR.xlsx
@@ -2064,11 +2064,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="48074097"/>
-        <c:axId val="85844360"/>
+        <c:axId val="22230553"/>
+        <c:axId val="23811093"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="48074097"/>
+        <c:axId val="22230553"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2100,7 +2100,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85844360"/>
+        <c:crossAx val="23811093"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
@@ -2111,7 +2111,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="85844360"/>
+        <c:axId val="23811093"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="90"/>
@@ -2185,7 +2185,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48074097"/>
+        <c:crossAx val="22230553"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
